--- a/allstats.xlsx
+++ b/allstats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e5g41\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9E968-099B-4524-82F4-50A5669B6902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21E8507-BAA9-4437-9FA7-EE8BFE73E3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="15" windowWidth="14325" windowHeight="12578" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Maximum packet length</t>
   </si>
   <si>
-    <t>Most common packet length</t>
-  </si>
-  <si>
     <t>Avg. packet interval</t>
   </si>
   <si>
@@ -84,6 +81,9 @@
   </si>
   <si>
     <t>Packet itvl variance</t>
+  </si>
+  <si>
+    <t>Packet length variance</t>
   </si>
 </sst>
 </file>
@@ -415,28 +415,28 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -471,7 +471,7 @@
         <v>2.021962342135152</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -506,7 +506,7 @@
         <v>4.8758801394983668E-2</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -541,7 +541,7 @@
         <v>2.1857517691324508E-2</v>
       </c>
       <c r="K4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -576,7 +576,7 @@
         <v>0.83866617373256291</v>
       </c>
       <c r="K5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -611,7 +611,7 @@
         <v>0.35616238512337789</v>
       </c>
       <c r="K6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -646,7 +646,7 @@
         <v>0.43637596025542136</v>
       </c>
       <c r="K7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -681,7 +681,7 @@
         <v>0.14357361714303518</v>
       </c>
       <c r="K8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -716,7 +716,7 @@
         <v>0.28159900614868905</v>
       </c>
       <c r="K9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
@@ -751,7 +751,7 @@
         <v>0.25839527964630005</v>
       </c>
       <c r="K10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
@@ -786,7 +786,7 @@
         <v>0.1349521040812921</v>
       </c>
       <c r="K11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -821,7 +821,7 @@
         <v>0.5684569706584236</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -856,7 +856,7 @@
         <v>3.1274291105476887E-2</v>
       </c>
       <c r="K13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -891,7 +891,7 @@
         <v>0.23603255582867699</v>
       </c>
       <c r="K14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -926,7 +926,7 @@
         <v>0.30238517657195041</v>
       </c>
       <c r="K15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
@@ -961,7 +961,7 @@
         <v>0.59334129249451795</v>
       </c>
       <c r="K16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
@@ -996,7 +996,7 @@
         <v>0.43143584517713018</v>
       </c>
       <c r="K17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
@@ -1031,7 +1031,7 @@
         <v>0.41294978204156219</v>
       </c>
       <c r="K18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
@@ -1066,7 +1066,7 @@
         <v>0.13881811501103056</v>
       </c>
       <c r="K19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
@@ -1101,7 +1101,7 @@
         <v>0.15973156070266586</v>
       </c>
       <c r="K20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
@@ -1136,7 +1136,7 @@
         <v>0.4721089761380432</v>
       </c>
       <c r="K21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
@@ -1171,7 +1171,7 @@
         <v>1.2497481362854923</v>
       </c>
       <c r="K22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
@@ -1206,7 +1206,7 @@
         <v>2.9440695414332061E-2</v>
       </c>
       <c r="K23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
@@ -1241,7 +1241,7 @@
         <v>0.29615795738576406</v>
       </c>
       <c r="K24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.45">
@@ -1276,7 +1276,7 @@
         <v>0.48959858992901323</v>
       </c>
       <c r="K25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.45">
@@ -1311,7 +1311,7 @@
         <v>0.1213008828122278</v>
       </c>
       <c r="K26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.45">
@@ -1346,7 +1346,7 @@
         <v>0.20573631397995334</v>
       </c>
       <c r="K27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.45">
@@ -1381,7 +1381,7 @@
         <v>0.10998075115018817</v>
       </c>
       <c r="K28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
@@ -1416,7 +1416,7 @@
         <v>1.7453064960753249E-2</v>
       </c>
       <c r="K29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
@@ -1451,7 +1451,7 @@
         <v>2.2020541700987599E-2</v>
       </c>
       <c r="K30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
@@ -1486,7 +1486,7 @@
         <v>0.11393292489763586</v>
       </c>
       <c r="K31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
@@ -1521,7 +1521,7 @@
         <v>8.9266150175720246E-2</v>
       </c>
       <c r="K32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
@@ -1556,7 +1556,7 @@
         <v>3.7539880585208333E-3</v>
       </c>
       <c r="K33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
@@ -1591,7 +1591,7 @@
         <v>6.7651219644758606E-2</v>
       </c>
       <c r="K34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
@@ -1626,7 +1626,7 @@
         <v>2.7120001702980609E-2</v>
       </c>
       <c r="K35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
@@ -1661,7 +1661,7 @@
         <v>2.3700430331741861E-2</v>
       </c>
       <c r="K36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
@@ -1696,7 +1696,7 @@
         <v>6.9733307881897503E-3</v>
       </c>
       <c r="K37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
@@ -1731,7 +1731,7 @@
         <v>3.7083549428667636E-2</v>
       </c>
       <c r="K38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
@@ -1766,7 +1766,7 @@
         <v>1.3830144233826412E-2</v>
       </c>
       <c r="K39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
@@ -1801,7 +1801,7 @@
         <v>9.0257677551948773E-2</v>
       </c>
       <c r="K40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
@@ -1836,7 +1836,7 @@
         <v>0.23301038075044056</v>
       </c>
       <c r="K41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
@@ -1871,7 +1871,7 @@
         <v>0.22782894011378887</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
@@ -1906,7 +1906,7 @@
         <v>1.1301831401408568E-2</v>
       </c>
       <c r="K43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
@@ -1941,7 +1941,7 @@
         <v>4.2339800356537317E-2</v>
       </c>
       <c r="K44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
@@ -1976,7 +1976,7 @@
         <v>6.9070980821640364E-3</v>
       </c>
       <c r="K45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
@@ -2011,7 +2011,7 @@
         <v>8.9151969164945983E-4</v>
       </c>
       <c r="K46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
@@ -2046,7 +2046,7 @@
         <v>1.5670547803379416E-3</v>
       </c>
       <c r="K47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
@@ -2081,7 +2081,7 @@
         <v>2.4178539248425231E-3</v>
       </c>
       <c r="K48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
@@ -2116,7 +2116,7 @@
         <v>4.4326308084015375E-3</v>
       </c>
       <c r="K49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
@@ -2151,7 +2151,7 @@
         <v>4.2884457827181933E-3</v>
       </c>
       <c r="K50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
@@ -2186,7 +2186,7 @@
         <v>3.8265206428285764E-2</v>
       </c>
       <c r="K51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
